--- a/olive-olove-listing.xlsx
+++ b/olive-olove-listing.xlsx
@@ -791,14 +791,14 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="M2" s="18" t="inlineStr">
-        <is>
-          <t>صابون بلدي من زيت الزيتون النقي وزيوت نباتية طبيعية، لتنظيف لطيف يترك البشرة ناعمة ورطبة. بالفحم الفعّال.</t>
-        </is>
-      </c>
-      <c r="N2" s="18" t="inlineStr">
-        <is>
-          <t>زيت زيتون، ماء، هيدروكسيد الصوديوم، زيت جوز الهند، الفحم الفعّال</t>
+      <c r="M2" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With activated charcoal.</t>
+        </is>
+      </c>
+      <c r="N2" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Olive oil, water, sodium hydroxide, coconut oil, activated charcoal</t>
         </is>
       </c>
       <c r="O2" s="14" t="inlineStr">
@@ -856,14 +856,14 @@
           <t>Coffee</t>
         </is>
       </c>
-      <c r="M3" s="18" t="inlineStr">
-        <is>
-          <t>صابون بلدي من زيت الزيتون النقي وزيوت نباتية طبيعية، لتنظيف لطيف يترك البشرة ناعمة ورطبة. ببودرة القهوة العربية، مقاوم للشيخوخة.</t>
-        </is>
-      </c>
-      <c r="N3" s="18" t="inlineStr">
-        <is>
-          <t>زيت زيتون، ماء، هيدروكسيد الصوديوم، زيت جوز الهند، بودرة القهوة العربية (فيتامين B3 النياسين)</t>
+      <c r="M3" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With Arabic coffee powder, anti-aging.</t>
+        </is>
+      </c>
+      <c r="N3" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Olive oil, water, sodium hydroxide, coconut oil, Arabic coffee powder (vitamin B3, niacin)</t>
         </is>
       </c>
       <c r="O3" s="14" t="inlineStr">
@@ -921,14 +921,14 @@
           <t>Curcum</t>
         </is>
       </c>
-      <c r="M4" s="18" t="inlineStr">
-        <is>
-          <t>صابون بلدي من زيت الزيتون النقي وزيوت نباتية طبيعية، لتنظيف لطيف يترك البشرة ناعمة ورطبة. ببودرة الكركم، لتفتيح البشرة.</t>
-        </is>
-      </c>
-      <c r="N4" s="18" t="inlineStr">
-        <is>
-          <t>زيت زيتون، ماء، هيدروكسيد الصوديوم، زيت جوز الهند، بودرة الكركم (فيتامين B، C)</t>
+      <c r="M4" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With turmeric powder, to brighten the skin.</t>
+        </is>
+      </c>
+      <c r="N4" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Olive oil, water, sodium hydroxide, coconut oil, turmeric powder (vitamins B and C)</t>
         </is>
       </c>
       <c r="O4" s="14" t="inlineStr">
@@ -986,14 +986,14 @@
           <t>Ghar</t>
         </is>
       </c>
-      <c r="M5" s="18" t="inlineStr">
-        <is>
-          <t>صابون بلدي من زيت الزيتون النقي وزيوت نباتية طبيعية، لتنظيف لطيف يترك البشرة ناعمة ورطبة. بمستخلص الغار وزيت الغار، مضيء للبشرة.</t>
-        </is>
-      </c>
-      <c r="N5" s="18" t="inlineStr">
-        <is>
-          <t>زيت زيتون، ماء، هيدروكسيد الصوديوم، زيت جوز الهند، مستخلص الغار (فيتامين B، C، K)، زيت الغار النقي (فيتامين A، E)</t>
+      <c r="M5" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With bay extract and pure bay oil, to brighten the skin.</t>
+        </is>
+      </c>
+      <c r="N5" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Olive oil, water, sodium hydroxide, coconut oil, bay extract (vitamins B, C, and K), pure bay oil (vitamins A and E)</t>
         </is>
       </c>
       <c r="O5" s="14" t="inlineStr">
@@ -1051,14 +1051,14 @@
           <t>Lavender</t>
         </is>
       </c>
-      <c r="M6" s="18" t="inlineStr">
-        <is>
-          <t>صابون بلدي من زيت الزيتون النقي وزيوت نباتية طبيعية، لتنظيف لطيف يترك البشرة ناعمة ورطبة. بمستخلص اللافندر وزيت اللافندر، ملطّف للبشرة.</t>
-        </is>
-      </c>
-      <c r="N6" s="18" t="inlineStr">
-        <is>
-          <t>زيت زيتون، ماء، هيدروكسيد الصوديوم، زيت جوز الهند، مستخلص اللافندر (فيتامين C)، زيت اللافندر النقي (فيتامين A، E)</t>
+      <c r="M6" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With lavender extract and pure lavender oil, to soothe the skin.</t>
+        </is>
+      </c>
+      <c r="N6" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Olive oil, water, sodium hydroxide, coconut oil, lavender extract (vitamin C), pure lavender oil (vitamins A and E)</t>
         </is>
       </c>
       <c r="O6" s="14" t="inlineStr">
@@ -1116,14 +1116,14 @@
           <t>Malva</t>
         </is>
       </c>
-      <c r="M7" s="18" t="inlineStr">
-        <is>
-          <t>صابون بلدي من زيت الزيتون النقي وزيوت نباتية طبيعية، لتنظيف لطيف يترك البشرة ناعمة ورطبة. بمستخلص الخبيزة، ملطّف.</t>
-        </is>
-      </c>
-      <c r="N7" s="18" t="inlineStr">
-        <is>
-          <t>زيت زيتون، ماء، هيدروكسيد الصوديوم، زيت جوز الهند، مستخلص الخبيزة (فيتامين A، B، C، E)</t>
+      <c r="M7" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With mallow extract, soothing.</t>
+        </is>
+      </c>
+      <c r="N7" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Olive oil, water, sodium hydroxide, coconut oil, mallow extract (vitamins A, B, C, and E)</t>
         </is>
       </c>
       <c r="O7" s="14" t="inlineStr">
@@ -1181,14 +1181,14 @@
           <t>Pitch White</t>
         </is>
       </c>
-      <c r="M8" s="18" t="inlineStr">
-        <is>
-          <t>صابون بلدي من زيت الزيتون النقي وزيوت نباتية طبيعية، لتنظيف لطيف يترك البشرة ناعمة ورطبة. بمخاط الحلزون والعسل والألوفيرا، غني بالفيتامينات.</t>
-        </is>
-      </c>
-      <c r="N8" s="18" t="inlineStr">
-        <is>
-          <t>زيت زيتون، ماء، هيدروكسيد الصوديوم، زيت جوز الهند، مخاط الحلزون (فيتامين A، C، E)، عسل، ألوفيرا</t>
+      <c r="M8" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With snail mucin, honey, and aloe vera, rich in vitamins.</t>
+        </is>
+      </c>
+      <c r="N8" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Olive oil, water, sodium hydroxide, coconut oil, snail mucin (vitamins A, C, and E), honey, aloe vera</t>
         </is>
       </c>
       <c r="O8" s="14" t="inlineStr">
@@ -1246,14 +1246,14 @@
           <t>The Miracle</t>
         </is>
       </c>
-      <c r="M9" s="18" t="inlineStr">
-        <is>
-          <t>صابون بلدي من زيت الزيتون النقي وزيوت نباتية طبيعية، لتنظيف لطيف يترك البشرة ناعمة ورطبة. بحليب أنثى الدابة، لتجديد البشرة.</t>
-        </is>
-      </c>
-      <c r="N9" s="18" t="inlineStr">
-        <is>
-          <t>زيت زيتون، ماء، هيدروكسيد الصوديوم، زيت جوز الهند، حليب أنثى الدابة (فيتامين A، B، C، D، E)</t>
+      <c r="M9" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With donkey milk, to renew the skin.</t>
+        </is>
+      </c>
+      <c r="N9" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Olive oil, water, sodium hydroxide, coconut oil, donkey milk (vitamins A, B, C, D, and E)</t>
         </is>
       </c>
       <c r="O9" s="14" t="inlineStr">
@@ -1311,14 +1311,14 @@
           <t>Coffee</t>
         </is>
       </c>
-      <c r="M10" s="18" t="inlineStr">
-        <is>
-          <t>سنفرة جسم من السكر والأملاح الغنية بالمعادن مع زيوت مغذية وفيتامين E، لبشرة ناعمة ومشرقة. رائحة قهوة.</t>
-        </is>
-      </c>
-      <c r="N10" s="18" t="inlineStr">
-        <is>
-          <t>سكر، ملح، ملح الهيمالايا، زيت جوز الهند، زيت بذور العنب، زيت الجوجوبا، زيت اللوز، زيت الخروع، قهوة، فيتامين E</t>
+      <c r="M10" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A body scrub of sugar and mineral-rich salts with nourishing oils and vitamin E, for soft, bright skin. Coffee scent.</t>
+        </is>
+      </c>
+      <c r="N10" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sugar, salt, Himalayan salt, coconut oil, grapeseed oil, jojoba oil, almond oil, castor oil, coffee, vitamin E</t>
         </is>
       </c>
       <c r="O10" s="14" t="inlineStr">
@@ -1376,14 +1376,14 @@
           <t>Dovey</t>
         </is>
       </c>
-      <c r="M11" s="18" t="inlineStr">
-        <is>
-          <t>سنفرة جسم من السكر والأملاح الغنية بالمعادن مع زيوت مغذية وفيتامين E، لبشرة ناعمة ومشرقة. رائحة دوفي.</t>
-        </is>
-      </c>
-      <c r="N11" s="18" t="inlineStr">
-        <is>
-          <t>سكر، ملح، ملح الهيمالايا، زيت جوز الهند، زيت بذور العنب، زيت الجوجوبا، زيت اللوز، زيت الخروع، عطر الدوفي، فيتامين E</t>
+      <c r="M11" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A body scrub of sugar and mineral-rich salts with nourishing oils and vitamin E, for soft, bright skin. Dovey scent.</t>
+        </is>
+      </c>
+      <c r="N11" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sugar, salt, Himalayan salt, coconut oil, grapeseed oil, jojoba oil, almond oil, castor oil, Dovey fragrance, vitamin E</t>
         </is>
       </c>
       <c r="O11" s="14" t="inlineStr">
@@ -1441,14 +1441,14 @@
           <t>Liligum</t>
         </is>
       </c>
-      <c r="M12" s="18" t="inlineStr">
-        <is>
-          <t>سنفرة جسم من السكر والأملاح الغنية بالمعادن مع زيوت مغذية وفيتامين E، لبشرة ناعمة ومشرقة. رائحة ليلي غام.</t>
-        </is>
-      </c>
-      <c r="N12" s="18" t="inlineStr">
-        <is>
-          <t>سكر، ملح، ملح الهيمالايا، زيت جوز الهند، زيت بذور العنب، زيت الجوجوبا، زيت اللوز، زيت الخروع، عطر الليلي غام، فيتامين E</t>
+      <c r="M12" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A body scrub of sugar and mineral-rich salts with nourishing oils and vitamin E, for soft, bright skin. Liligum scent.</t>
+        </is>
+      </c>
+      <c r="N12" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sugar, salt, Himalayan salt, coconut oil, grapeseed oil, jojoba oil, almond oil, castor oil, Liligum fragrance, vitamin E</t>
         </is>
       </c>
       <c r="O12" s="14" t="inlineStr">
@@ -1506,14 +1506,14 @@
           <t>Misk</t>
         </is>
       </c>
-      <c r="M13" s="18" t="inlineStr">
-        <is>
-          <t>سنفرة جسم من السكر والأملاح الغنية بالمعادن مع زيوت مغذية وفيتامين E، لبشرة ناعمة ومشرقة. رائحة مسك.</t>
-        </is>
-      </c>
-      <c r="N13" s="18" t="inlineStr">
-        <is>
-          <t>سكر، ملح، ملح الهيمالايا، زيت جوز الهند، زيت بذور العنب، زيت الجوجوبا، زيت اللوز، زيت الخروع، عطر المسك، فيتامين E</t>
+      <c r="M13" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A body scrub of sugar and mineral-rich salts with nourishing oils and vitamin E, for soft, bright skin. Musk scent.</t>
+        </is>
+      </c>
+      <c r="N13" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sugar, salt, Himalayan salt, coconut oil, grapeseed oil, jojoba oil, almond oil, castor oil, musk fragrance, vitamin E</t>
         </is>
       </c>
       <c r="O13" s="14" t="inlineStr">
@@ -1571,14 +1571,14 @@
           <t>Oak</t>
         </is>
       </c>
-      <c r="M14" s="18" t="inlineStr">
-        <is>
-          <t>سنفرة جسم من السكر والأملاح الغنية بالمعادن مع زيوت مغذية وفيتامين E، لبشرة ناعمة ومشرقة. رائحة سنديان.</t>
-        </is>
-      </c>
-      <c r="N14" s="18" t="inlineStr">
-        <is>
-          <t>سكر، ملح، ملح الهيمالايا، زيت جوز الهند، زيت بذور العنب، زيت الجوجوبا، زيت اللوز، زيت الخروع، عطر السنديان، فيتامين E</t>
+      <c r="M14" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A body scrub of sugar and mineral-rich salts with nourishing oils and vitamin E, for soft, bright skin. Oak scent.</t>
+        </is>
+      </c>
+      <c r="N14" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sugar, salt, Himalayan salt, coconut oil, grapeseed oil, jojoba oil, almond oil, castor oil, oak fragrance, vitamin E</t>
         </is>
       </c>
       <c r="O14" s="14" t="inlineStr">
@@ -1636,14 +1636,14 @@
           <t>Oud</t>
         </is>
       </c>
-      <c r="M15" s="18" t="inlineStr">
-        <is>
-          <t>سنفرة جسم من السكر والأملاح الغنية بالمعادن مع زيوت مغذية وفيتامين E، لبشرة ناعمة ومشرقة. رائحة عود.</t>
-        </is>
-      </c>
-      <c r="N15" s="18" t="inlineStr">
-        <is>
-          <t>سكر، ملح، ملح الهيمالايا، زيت جوز الهند، زيت بذور العنب، زيت الجوجوبا، زيت اللوز، زيت الخروع، عطر العود، فيتامين E</t>
+      <c r="M15" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A body scrub of sugar and mineral-rich salts with nourishing oils and vitamin E, for soft, bright skin. Oud scent.</t>
+        </is>
+      </c>
+      <c r="N15" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sugar, salt, Himalayan salt, coconut oil, grapeseed oil, jojoba oil, almond oil, castor oil, oud fragrance, vitamin E</t>
         </is>
       </c>
       <c r="O15" s="14" t="inlineStr">
@@ -1701,14 +1701,14 @@
           <t>Dovey</t>
         </is>
       </c>
-      <c r="M16" s="18" t="inlineStr">
-        <is>
-          <t>صابون سائل من زيت الزيتون وزيت جوز الهند، ينظّف البشرة ويحافظ على نعومتها برغوة خفيفة. رائحة دوفي.</t>
-        </is>
-      </c>
-      <c r="N16" s="18" t="inlineStr">
-        <is>
-          <t>زيت زيتون، زيت جوز الهند، هيدروكسيد البوتاسيوم، ماء، عطر الدوفي</t>
+      <c r="M16" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A liquid soap of olive oil and coconut oil that cleanses the skin and keeps it soft with a light lather. Dovey scent.</t>
+        </is>
+      </c>
+      <c r="N16" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Olive oil, coconut oil, potassium hydroxide, water, Dovey fragrance</t>
         </is>
       </c>
       <c r="O16" s="14" t="inlineStr">
@@ -1766,14 +1766,14 @@
           <t>Lavender</t>
         </is>
       </c>
-      <c r="M17" s="18" t="inlineStr">
-        <is>
-          <t>صابون سائل من زيت الزيتون وزيت جوز الهند، ينظّف البشرة ويحافظ على نعومتها برغوة خفيفة. رائحة لافندر.</t>
-        </is>
-      </c>
-      <c r="N17" s="18" t="inlineStr">
-        <is>
-          <t>زيت زيتون، زيت جوز الهند، هيدروكسيد البوتاسيوم، ماء، عطر اللافندر</t>
+      <c r="M17" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A liquid soap of olive oil and coconut oil that cleanses the skin and keeps it soft with a light lather. Lavender scent.</t>
+        </is>
+      </c>
+      <c r="N17" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Olive oil, coconut oil, potassium hydroxide, water, lavender fragrance</t>
         </is>
       </c>
       <c r="O17" s="14" t="inlineStr">
@@ -1831,14 +1831,14 @@
           <t>Misk</t>
         </is>
       </c>
-      <c r="M18" s="18" t="inlineStr">
-        <is>
-          <t>صابون سائل من زيت الزيتون وزيت جوز الهند، ينظّف البشرة ويحافظ على نعومتها برغوة خفيفة. رائحة مسك.</t>
-        </is>
-      </c>
-      <c r="N18" s="18" t="inlineStr">
-        <is>
-          <t>زيت زيتون، زيت جوز الهند، هيدروكسيد البوتاسيوم، ماء، عطر المسك</t>
+      <c r="M18" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A liquid soap of olive oil and coconut oil that cleanses the skin and keeps it soft with a light lather. Musk scent.</t>
+        </is>
+      </c>
+      <c r="N18" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Olive oil, coconut oil, potassium hydroxide, water, musk fragrance</t>
         </is>
       </c>
       <c r="O18" s="14" t="inlineStr">
@@ -1896,14 +1896,14 @@
           <t>Oud</t>
         </is>
       </c>
-      <c r="M19" s="18" t="inlineStr">
-        <is>
-          <t>صابون سائل من زيت الزيتون وزيت جوز الهند، ينظّف البشرة ويحافظ على نعومتها برغوة خفيفة. رائحة عود.</t>
-        </is>
-      </c>
-      <c r="N19" s="18" t="inlineStr">
-        <is>
-          <t>زيت زيتون، زيت جوز الهند، هيدروكسيد البوتاسيوم، ماء، عطر العود</t>
+      <c r="M19" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A liquid soap of olive oil and coconut oil that cleanses the skin and keeps it soft with a light lather. Oud scent.</t>
+        </is>
+      </c>
+      <c r="N19" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Olive oil, coconut oil, potassium hydroxide, water, oud fragrance</t>
         </is>
       </c>
       <c r="O19" s="14" t="inlineStr">
@@ -1961,14 +1961,14 @@
           <t>Oak</t>
         </is>
       </c>
-      <c r="M20" s="18" t="inlineStr">
-        <is>
-          <t>صابون سائل من زيت الزيتون وزيت جوز الهند، ينظّف البشرة ويحافظ على نعومتها برغوة خفيفة. رائحة سنديان.</t>
-        </is>
-      </c>
-      <c r="N20" s="18" t="inlineStr">
-        <is>
-          <t>زيت زيتون، زيت جوز الهند، هيدروكسيد البوتاسيوم، ماء، عطر السنديان</t>
+      <c r="M20" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A liquid soap of olive oil and coconut oil that cleanses the skin and keeps it soft with a light lather. Oak scent.</t>
+        </is>
+      </c>
+      <c r="N20" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Olive oil, coconut oil, potassium hydroxide, water, oak fragrance</t>
         </is>
       </c>
       <c r="O20" s="14" t="inlineStr">
@@ -2026,14 +2026,14 @@
           <t>Dovey</t>
         </is>
       </c>
-      <c r="M21" s="18" t="inlineStr">
-        <is>
-          <t>جل استحمام خفيف من زيت الزيتون وجوز الهند واللوز الحلو والخروع، ينظّف البشرة ويبقيها ناعمة ورطبة. رائحة دوفي.</t>
-        </is>
-      </c>
-      <c r="N21" s="18" t="inlineStr">
-        <is>
-          <t>زيت زيتون، زيت جوز الهند، زيت اللوز الحلو، زيت الخروع، هيدروكسيد البوتاسيوم، ماء، عطر دوفي</t>
+      <c r="M21" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A light shower gel of olive oil, coconut, sweet almond, and castor oil. It cleanses the skin and leaves it soft and moisturized. Dovey scent.</t>
+        </is>
+      </c>
+      <c r="N21" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Olive oil, coconut oil, sweet almond oil, castor oil, potassium hydroxide, water, Dovey fragrance</t>
         </is>
       </c>
       <c r="O21" s="14" t="inlineStr">
@@ -2091,14 +2091,14 @@
           <t>Liligum</t>
         </is>
       </c>
-      <c r="M22" s="18" t="inlineStr">
-        <is>
-          <t>جل استحمام خفيف من زيت الزيتون وجوز الهند واللوز الحلو والخروع، ينظّف البشرة ويبقيها ناعمة ورطبة. رائحة ليلي غام.</t>
-        </is>
-      </c>
-      <c r="N22" s="18" t="inlineStr">
-        <is>
-          <t>زيت زيتون، زيت جوز الهند، زيت اللوز الحلو، زيت الخروع، هيدروكسيد البوتاسيوم، ماء، عطر الليلي غام</t>
+      <c r="M22" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A light shower gel of olive oil, coconut, sweet almond, and castor oil. It cleanses the skin and leaves it soft and moisturized. Liligum scent.</t>
+        </is>
+      </c>
+      <c r="N22" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Olive oil, coconut oil, sweet almond oil, castor oil, potassium hydroxide, water, Liligum fragrance</t>
         </is>
       </c>
       <c r="O22" s="14" t="inlineStr">
@@ -2156,14 +2156,14 @@
           <t>Misk</t>
         </is>
       </c>
-      <c r="M23" s="18" t="inlineStr">
-        <is>
-          <t>جل استحمام خفيف من زيت الزيتون وجوز الهند واللوز الحلو والخروع، ينظّف البشرة ويبقيها ناعمة ورطبة. رائحة مسك.</t>
-        </is>
-      </c>
-      <c r="N23" s="18" t="inlineStr">
-        <is>
-          <t>زيت زيتون، زيت جوز الهند، زيت اللوز الحلو، زيت الخروع، هيدروكسيد البوتاسيوم، ماء، عطر المسك</t>
+      <c r="M23" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A light shower gel of olive oil, coconut, sweet almond, and castor oil. It cleanses the skin and leaves it soft and moisturized. Musk scent.</t>
+        </is>
+      </c>
+      <c r="N23" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Olive oil, coconut oil, sweet almond oil, castor oil, potassium hydroxide, water, musk fragrance</t>
         </is>
       </c>
       <c r="O23" s="14" t="inlineStr">
@@ -2221,14 +2221,14 @@
           <t>Oak</t>
         </is>
       </c>
-      <c r="M24" s="18" t="inlineStr">
-        <is>
-          <t>جل استحمام خفيف من زيت الزيتون وجوز الهند واللوز الحلو والخروع، ينظّف البشرة ويبقيها ناعمة ورطبة. رائحة سنديان.</t>
-        </is>
-      </c>
-      <c r="N24" s="18" t="inlineStr">
-        <is>
-          <t>زيت زيتون، زيت جوز الهند، زيت اللوز الحلو، زيت الخروع، هيدروكسيد البوتاسيوم، ماء، عطر السنديان</t>
+      <c r="M24" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A light shower gel of olive oil, coconut, sweet almond, and castor oil. It cleanses the skin and leaves it soft and moisturized. Oak scent.</t>
+        </is>
+      </c>
+      <c r="N24" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Olive oil, coconut oil, sweet almond oil, castor oil, potassium hydroxide, water, oak fragrance</t>
         </is>
       </c>
       <c r="O24" s="14" t="inlineStr">
@@ -2286,14 +2286,14 @@
           <t>Oud</t>
         </is>
       </c>
-      <c r="M25" s="18" t="inlineStr">
-        <is>
-          <t>جل استحمام خفيف من زيت الزيتون وجوز الهند واللوز الحلو والخروع، ينظّف البشرة ويبقيها ناعمة ورطبة. رائحة عود.</t>
-        </is>
-      </c>
-      <c r="N25" s="18" t="inlineStr">
-        <is>
-          <t>زيت زيتون، زيت جوز الهند، زيت اللوز الحلو، زيت الخروع، هيدروكسيد البوتاسيوم، ماء، عطر العود</t>
+      <c r="M25" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A light shower gel of olive oil, coconut, sweet almond, and castor oil. It cleanses the skin and leaves it soft and moisturized. Oud scent.</t>
+        </is>
+      </c>
+      <c r="N25" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Olive oil, coconut oil, sweet almond oil, castor oil, potassium hydroxide, water, oud fragrance</t>
         </is>
       </c>
       <c r="O25" s="14" t="inlineStr">

--- a/olive-olove-listing.xlsx
+++ b/olive-olove-listing.xlsx
@@ -647,7 +647,7 @@
   <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="11.5546875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="10.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="8.5546875" customWidth="1" min="4" max="4"/>
@@ -743,6 +743,11 @@
       <c r="P1" s="12" t="n"/>
     </row>
     <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>225531799198</t>
+        </is>
+      </c>
       <c r="B2" s="14" t="n">
         <v>41</v>
       </c>
@@ -808,6 +813,11 @@
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>515128602366</t>
+        </is>
+      </c>
       <c r="B3" s="14" t="n">
         <v>42</v>
       </c>
@@ -873,6 +883,11 @@
       </c>
     </row>
     <row r="4" ht="48" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>503496785239</t>
+        </is>
+      </c>
       <c r="B4" s="14" t="n">
         <v>43</v>
       </c>
@@ -938,6 +953,11 @@
       </c>
     </row>
     <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>249053004401</t>
+        </is>
+      </c>
       <c r="B5" s="14" t="n">
         <v>44</v>
       </c>
@@ -1003,6 +1023,11 @@
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>729938168107</t>
+        </is>
+      </c>
       <c r="B6" s="14" t="n">
         <v>45</v>
       </c>
@@ -1133,6 +1158,11 @@
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>743686724757</t>
+        </is>
+      </c>
       <c r="B8" s="14" t="n">
         <v>47</v>
       </c>
@@ -1198,6 +1228,11 @@
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>248073092460</t>
+        </is>
+      </c>
       <c r="B9" s="14" t="n">
         <v>48</v>
       </c>
@@ -1263,6 +1298,11 @@
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>902445893535</t>
+        </is>
+      </c>
       <c r="B10" s="14" t="n">
         <v>23</v>
       </c>
@@ -1328,6 +1368,11 @@
       </c>
     </row>
     <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>614330363588</t>
+        </is>
+      </c>
       <c r="B11" s="14" t="n">
         <v>21</v>
       </c>
@@ -1393,6 +1438,11 @@
       </c>
     </row>
     <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>656965689469</t>
+        </is>
+      </c>
       <c r="B12" s="14" t="n">
         <v>22</v>
       </c>
@@ -1458,6 +1508,11 @@
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>161481058975</t>
+        </is>
+      </c>
       <c r="B13" s="14" t="n">
         <v>26</v>
       </c>
@@ -1523,6 +1578,11 @@
       </c>
     </row>
     <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>667449289869</t>
+        </is>
+      </c>
       <c r="B14" s="14" t="n">
         <v>25</v>
       </c>
@@ -1588,6 +1648,11 @@
       </c>
     </row>
     <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>907164993630</t>
+        </is>
+      </c>
       <c r="B15" s="14" t="n">
         <v>24</v>
       </c>
@@ -1653,6 +1718,11 @@
       </c>
     </row>
     <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>558465371428</t>
+        </is>
+      </c>
       <c r="B16" s="14" t="n">
         <v>31</v>
       </c>
@@ -1718,6 +1788,11 @@
       </c>
     </row>
     <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>571503845006</t>
+        </is>
+      </c>
       <c r="B17" s="14" t="n">
         <v>32</v>
       </c>
@@ -1783,6 +1858,11 @@
       </c>
     </row>
     <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>869913122129</t>
+        </is>
+      </c>
       <c r="B18" s="14" t="n">
         <v>35</v>
       </c>
@@ -1848,6 +1928,11 @@
       </c>
     </row>
     <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>883989092945</t>
+        </is>
+      </c>
       <c r="B19" s="14" t="n">
         <v>33</v>
       </c>
@@ -1913,6 +1998,11 @@
       </c>
     </row>
     <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>756293758373</t>
+        </is>
+      </c>
       <c r="B20" s="14" t="n">
         <v>34</v>
       </c>
@@ -1978,6 +2068,11 @@
       </c>
     </row>
     <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>710078629506</t>
+        </is>
+      </c>
       <c r="B21" s="14" t="n">
         <v>11</v>
       </c>
@@ -2043,6 +2138,11 @@
       </c>
     </row>
     <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>909285146339</t>
+        </is>
+      </c>
       <c r="B22" s="14" t="n">
         <v>12</v>
       </c>
@@ -2108,6 +2208,11 @@
       </c>
     </row>
     <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>549874834222</t>
+        </is>
+      </c>
       <c r="B23" s="14" t="n">
         <v>15</v>
       </c>
@@ -2173,6 +2278,11 @@
       </c>
     </row>
     <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>537824641738</t>
+        </is>
+      </c>
       <c r="B24" s="14" t="n">
         <v>14</v>
       </c>
@@ -2238,6 +2348,11 @@
       </c>
     </row>
     <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>889082131939</t>
+        </is>
+      </c>
       <c r="B25" s="14" t="n">
         <v>13</v>
       </c>

--- a/olive-olove-listing.xlsx
+++ b/olive-olove-listing.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_([$KWD]\ * #,##0.000_);_([$KWD]\ * \(#,##0.000\);_([$KWD]\ * &quot;-&quot;???_);_(@_)"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -46,6 +46,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -142,7 +147,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -195,6 +200,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -647,7 +655,7 @@
   <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="10.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="8.5546875" customWidth="1" min="4" max="4"/>
@@ -743,7 +751,7 @@
       <c r="P1" s="12" t="n"/>
     </row>
     <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>225531799198</t>
         </is>
@@ -798,12 +806,12 @@
       </c>
       <c r="M2" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With activated charcoal.</t>
+          <t>A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With activated charcoal.</t>
         </is>
       </c>
       <c r="N2" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olive oil, water, sodium hydroxide, coconut oil, activated charcoal</t>
+          <t>Olive oil, water, sodium hydroxide, coconut oil, activated charcoal</t>
         </is>
       </c>
       <c r="O2" s="14" t="inlineStr">
@@ -813,7 +821,7 @@
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>515128602366</t>
         </is>
@@ -868,12 +876,12 @@
       </c>
       <c r="M3" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With Arabic coffee powder, anti-aging.</t>
+          <t>A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With Arabic coffee powder, anti-aging.</t>
         </is>
       </c>
       <c r="N3" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olive oil, water, sodium hydroxide, coconut oil, Arabic coffee powder (vitamin B3, niacin)</t>
+          <t>Olive oil, water, sodium hydroxide, coconut oil, Arabic coffee powder (vitamin B3, niacin)</t>
         </is>
       </c>
       <c r="O3" s="14" t="inlineStr">
@@ -883,7 +891,7 @@
       </c>
     </row>
     <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>503496785239</t>
         </is>
@@ -938,12 +946,12 @@
       </c>
       <c r="M4" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With turmeric powder, to brighten the skin.</t>
+          <t>A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With turmeric powder, to brighten the skin.</t>
         </is>
       </c>
       <c r="N4" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olive oil, water, sodium hydroxide, coconut oil, turmeric powder (vitamins B and C)</t>
+          <t>Olive oil, water, sodium hydroxide, coconut oil, turmeric powder (vitamins B and C)</t>
         </is>
       </c>
       <c r="O4" s="14" t="inlineStr">
@@ -953,7 +961,7 @@
       </c>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>249053004401</t>
         </is>
@@ -1008,12 +1016,12 @@
       </c>
       <c r="M5" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With bay extract and pure bay oil, to brighten the skin.</t>
+          <t>A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With bay extract and pure bay oil, to brighten the skin.</t>
         </is>
       </c>
       <c r="N5" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olive oil, water, sodium hydroxide, coconut oil, bay extract (vitamins B, C, and K), pure bay oil (vitamins A and E)</t>
+          <t>Olive oil, water, sodium hydroxide, coconut oil, bay extract (vitamins B, C, and K), pure bay oil (vitamins A and E)</t>
         </is>
       </c>
       <c r="O5" s="14" t="inlineStr">
@@ -1023,7 +1031,7 @@
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>729938168107</t>
         </is>
@@ -1078,12 +1086,12 @@
       </c>
       <c r="M6" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With lavender extract and pure lavender oil, to soothe the skin.</t>
+          <t>A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With lavender extract and pure lavender oil, to soothe the skin.</t>
         </is>
       </c>
       <c r="N6" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olive oil, water, sodium hydroxide, coconut oil, lavender extract (vitamin C), pure lavender oil (vitamins A and E)</t>
+          <t>Olive oil, water, sodium hydroxide, coconut oil, lavender extract (vitamin C), pure lavender oil (vitamins A and E)</t>
         </is>
       </c>
       <c r="O6" s="14" t="inlineStr">
@@ -1093,6 +1101,7 @@
       </c>
     </row>
     <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="19" t="n"/>
       <c r="B7" s="14" t="n">
         <v>46</v>
       </c>
@@ -1143,12 +1152,12 @@
       </c>
       <c r="M7" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With mallow extract, soothing.</t>
+          <t>A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With mallow extract, soothing.</t>
         </is>
       </c>
       <c r="N7" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olive oil, water, sodium hydroxide, coconut oil, mallow extract (vitamins A, B, C, and E)</t>
+          <t>Olive oil, water, sodium hydroxide, coconut oil, mallow extract (vitamins A, B, C, and E)</t>
         </is>
       </c>
       <c r="O7" s="14" t="inlineStr">
@@ -1158,7 +1167,7 @@
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>743686724757</t>
         </is>
@@ -1213,12 +1222,12 @@
       </c>
       <c r="M8" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With snail mucin, honey, and aloe vera, rich in vitamins.</t>
+          <t>A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With snail mucin, honey, and aloe vera, rich in vitamins.</t>
         </is>
       </c>
       <c r="N8" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olive oil, water, sodium hydroxide, coconut oil, snail mucin (vitamins A, C, and E), honey, aloe vera</t>
+          <t>Olive oil, water, sodium hydroxide, coconut oil, snail mucin (vitamins A, C, and E), honey, aloe vera</t>
         </is>
       </c>
       <c r="O8" s="14" t="inlineStr">
@@ -1228,7 +1237,7 @@
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>248073092460</t>
         </is>
@@ -1283,12 +1292,12 @@
       </c>
       <c r="M9" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With donkey milk, to renew the skin.</t>
+          <t>A traditional bar soap of pure olive oil and natural plant oils, for a gentle cleanse that leaves the skin soft and moisturized. With donkey milk, to renew the skin.</t>
         </is>
       </c>
       <c r="N9" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olive oil, water, sodium hydroxide, coconut oil, donkey milk (vitamins A, B, C, D, and E)</t>
+          <t>Olive oil, water, sodium hydroxide, coconut oil, donkey milk (vitamins A, B, C, D, and E)</t>
         </is>
       </c>
       <c r="O9" s="14" t="inlineStr">
@@ -1298,7 +1307,7 @@
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>902445893535</t>
         </is>
@@ -1353,12 +1362,12 @@
       </c>
       <c r="M10" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A body scrub of sugar and mineral-rich salts with nourishing oils and vitamin E, for soft, bright skin. Coffee scent.</t>
+          <t>A body scrub of sugar and mineral-rich salts with nourishing oils and vitamin E, for soft, bright skin. Coffee scent.</t>
         </is>
       </c>
       <c r="N10" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sugar, salt, Himalayan salt, coconut oil, grapeseed oil, jojoba oil, almond oil, castor oil, coffee, vitamin E</t>
+          <t>Sugar, salt, Himalayan salt, coconut oil, grapeseed oil, jojoba oil, almond oil, castor oil, coffee, vitamin E</t>
         </is>
       </c>
       <c r="O10" s="14" t="inlineStr">
@@ -1368,7 +1377,7 @@
       </c>
     </row>
     <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>614330363588</t>
         </is>
@@ -1423,12 +1432,12 @@
       </c>
       <c r="M11" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A body scrub of sugar and mineral-rich salts with nourishing oils and vitamin E, for soft, bright skin. Dovey scent.</t>
+          <t>A body scrub of sugar and mineral-rich salts with nourishing oils and vitamin E, for soft, bright skin. Dovey scent.</t>
         </is>
       </c>
       <c r="N11" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sugar, salt, Himalayan salt, coconut oil, grapeseed oil, jojoba oil, almond oil, castor oil, Dovey fragrance, vitamin E</t>
+          <t>Sugar, salt, Himalayan salt, coconut oil, grapeseed oil, jojoba oil, almond oil, castor oil, Dovey fragrance, vitamin E</t>
         </is>
       </c>
       <c r="O11" s="14" t="inlineStr">
@@ -1438,7 +1447,7 @@
       </c>
     </row>
     <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>656965689469</t>
         </is>
@@ -1493,12 +1502,12 @@
       </c>
       <c r="M12" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A body scrub of sugar and mineral-rich salts with nourishing oils and vitamin E, for soft, bright skin. Liligum scent.</t>
+          <t>A body scrub of sugar and mineral-rich salts with nourishing oils and vitamin E, for soft, bright skin. Liligum scent.</t>
         </is>
       </c>
       <c r="N12" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sugar, salt, Himalayan salt, coconut oil, grapeseed oil, jojoba oil, almond oil, castor oil, Liligum fragrance, vitamin E</t>
+          <t>Sugar, salt, Himalayan salt, coconut oil, grapeseed oil, jojoba oil, almond oil, castor oil, Liligum fragrance, vitamin E</t>
         </is>
       </c>
       <c r="O12" s="14" t="inlineStr">
@@ -1508,7 +1517,7 @@
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>161481058975</t>
         </is>
@@ -1563,12 +1572,12 @@
       </c>
       <c r="M13" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A body scrub of sugar and mineral-rich salts with nourishing oils and vitamin E, for soft, bright skin. Musk scent.</t>
+          <t>A body scrub of sugar and mineral-rich salts with nourishing oils and vitamin E, for soft, bright skin. Musk scent.</t>
         </is>
       </c>
       <c r="N13" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sugar, salt, Himalayan salt, coconut oil, grapeseed oil, jojoba oil, almond oil, castor oil, musk fragrance, vitamin E</t>
+          <t>Sugar, salt, Himalayan salt, coconut oil, grapeseed oil, jojoba oil, almond oil, castor oil, musk fragrance, vitamin E</t>
         </is>
       </c>
       <c r="O13" s="14" t="inlineStr">
@@ -1578,7 +1587,7 @@
       </c>
     </row>
     <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>667449289869</t>
         </is>
@@ -1633,12 +1642,12 @@
       </c>
       <c r="M14" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A body scrub of sugar and mineral-rich salts with nourishing oils and vitamin E, for soft, bright skin. Oak scent.</t>
+          <t>A body scrub of sugar and mineral-rich salts with nourishing oils and vitamin E, for soft, bright skin. Oak scent.</t>
         </is>
       </c>
       <c r="N14" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sugar, salt, Himalayan salt, coconut oil, grapeseed oil, jojoba oil, almond oil, castor oil, oak fragrance, vitamin E</t>
+          <t>Sugar, salt, Himalayan salt, coconut oil, grapeseed oil, jojoba oil, almond oil, castor oil, oak fragrance, vitamin E</t>
         </is>
       </c>
       <c r="O14" s="14" t="inlineStr">
@@ -1648,7 +1657,7 @@
       </c>
     </row>
     <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>907164993630</t>
         </is>
@@ -1703,12 +1712,12 @@
       </c>
       <c r="M15" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A body scrub of sugar and mineral-rich salts with nourishing oils and vitamin E, for soft, bright skin. Oud scent.</t>
+          <t>A body scrub of sugar and mineral-rich salts with nourishing oils and vitamin E, for soft, bright skin. Oud scent.</t>
         </is>
       </c>
       <c r="N15" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sugar, salt, Himalayan salt, coconut oil, grapeseed oil, jojoba oil, almond oil, castor oil, oud fragrance, vitamin E</t>
+          <t>Sugar, salt, Himalayan salt, coconut oil, grapeseed oil, jojoba oil, almond oil, castor oil, oud fragrance, vitamin E</t>
         </is>
       </c>
       <c r="O15" s="14" t="inlineStr">
@@ -1718,7 +1727,7 @@
       </c>
     </row>
     <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>558465371428</t>
         </is>
@@ -1773,12 +1782,12 @@
       </c>
       <c r="M16" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A liquid soap of olive oil and coconut oil that cleanses the skin and keeps it soft with a light lather. Dovey scent.</t>
+          <t>A liquid soap of olive oil and coconut oil that cleanses the skin and keeps it soft with a light lather. Dovey scent.</t>
         </is>
       </c>
       <c r="N16" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olive oil, coconut oil, potassium hydroxide, water, Dovey fragrance</t>
+          <t>Olive oil, coconut oil, potassium hydroxide, water, Dovey fragrance</t>
         </is>
       </c>
       <c r="O16" s="14" t="inlineStr">
@@ -1788,7 +1797,7 @@
       </c>
     </row>
     <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>571503845006</t>
         </is>
@@ -1843,12 +1852,12 @@
       </c>
       <c r="M17" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A liquid soap of olive oil and coconut oil that cleanses the skin and keeps it soft with a light lather. Lavender scent.</t>
+          <t>A liquid soap of olive oil and coconut oil that cleanses the skin and keeps it soft with a light lather. Lavender scent.</t>
         </is>
       </c>
       <c r="N17" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olive oil, coconut oil, potassium hydroxide, water, lavender fragrance</t>
+          <t>Olive oil, coconut oil, potassium hydroxide, water, lavender fragrance</t>
         </is>
       </c>
       <c r="O17" s="14" t="inlineStr">
@@ -1858,7 +1867,7 @@
       </c>
     </row>
     <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>869913122129</t>
         </is>
@@ -1913,12 +1922,12 @@
       </c>
       <c r="M18" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A liquid soap of olive oil and coconut oil that cleanses the skin and keeps it soft with a light lather. Musk scent.</t>
+          <t>A liquid soap of olive oil and coconut oil that cleanses the skin and keeps it soft with a light lather. Musk scent.</t>
         </is>
       </c>
       <c r="N18" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olive oil, coconut oil, potassium hydroxide, water, musk fragrance</t>
+          <t>Olive oil, coconut oil, potassium hydroxide, water, musk fragrance</t>
         </is>
       </c>
       <c r="O18" s="14" t="inlineStr">
@@ -1928,7 +1937,7 @@
       </c>
     </row>
     <row r="19" ht="48" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>883989092945</t>
         </is>
@@ -1983,12 +1992,12 @@
       </c>
       <c r="M19" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A liquid soap of olive oil and coconut oil that cleanses the skin and keeps it soft with a light lather. Oud scent.</t>
+          <t>A liquid soap of olive oil and coconut oil that cleanses the skin and keeps it soft with a light lather. Oud scent.</t>
         </is>
       </c>
       <c r="N19" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olive oil, coconut oil, potassium hydroxide, water, oud fragrance</t>
+          <t>Olive oil, coconut oil, potassium hydroxide, water, oud fragrance</t>
         </is>
       </c>
       <c r="O19" s="14" t="inlineStr">
@@ -1998,7 +2007,7 @@
       </c>
     </row>
     <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>756293758373</t>
         </is>
@@ -2053,12 +2062,12 @@
       </c>
       <c r="M20" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A liquid soap of olive oil and coconut oil that cleanses the skin and keeps it soft with a light lather. Oak scent.</t>
+          <t>A liquid soap of olive oil and coconut oil that cleanses the skin and keeps it soft with a light lather. Oak scent.</t>
         </is>
       </c>
       <c r="N20" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olive oil, coconut oil, potassium hydroxide, water, oak fragrance</t>
+          <t>Olive oil, coconut oil, potassium hydroxide, water, oak fragrance</t>
         </is>
       </c>
       <c r="O20" s="14" t="inlineStr">
@@ -2068,7 +2077,7 @@
       </c>
     </row>
     <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>710078629506</t>
         </is>
@@ -2123,12 +2132,12 @@
       </c>
       <c r="M21" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A light shower gel of olive oil, coconut, sweet almond, and castor oil. It cleanses the skin and leaves it soft and moisturized. Dovey scent.</t>
+          <t>A light shower gel of olive oil, coconut, sweet almond, and castor oil. It cleanses the skin and leaves it soft and moisturized. Dovey scent.</t>
         </is>
       </c>
       <c r="N21" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olive oil, coconut oil, sweet almond oil, castor oil, potassium hydroxide, water, Dovey fragrance</t>
+          <t>Olive oil, coconut oil, sweet almond oil, castor oil, potassium hydroxide, water, Dovey fragrance</t>
         </is>
       </c>
       <c r="O21" s="14" t="inlineStr">
@@ -2138,7 +2147,7 @@
       </c>
     </row>
     <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>909285146339</t>
         </is>
@@ -2193,12 +2202,12 @@
       </c>
       <c r="M22" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A light shower gel of olive oil, coconut, sweet almond, and castor oil. It cleanses the skin and leaves it soft and moisturized. Liligum scent.</t>
+          <t>A light shower gel of olive oil, coconut, sweet almond, and castor oil. It cleanses the skin and leaves it soft and moisturized. Liligum scent.</t>
         </is>
       </c>
       <c r="N22" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olive oil, coconut oil, sweet almond oil, castor oil, potassium hydroxide, water, Liligum fragrance</t>
+          <t>Olive oil, coconut oil, sweet almond oil, castor oil, potassium hydroxide, water, Liligum fragrance</t>
         </is>
       </c>
       <c r="O22" s="14" t="inlineStr">
@@ -2208,7 +2217,7 @@
       </c>
     </row>
     <row r="23" ht="48" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>549874834222</t>
         </is>
@@ -2263,12 +2272,12 @@
       </c>
       <c r="M23" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A light shower gel of olive oil, coconut, sweet almond, and castor oil. It cleanses the skin and leaves it soft and moisturized. Musk scent.</t>
+          <t>A light shower gel of olive oil, coconut, sweet almond, and castor oil. It cleanses the skin and leaves it soft and moisturized. Musk scent.</t>
         </is>
       </c>
       <c r="N23" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olive oil, coconut oil, sweet almond oil, castor oil, potassium hydroxide, water, musk fragrance</t>
+          <t>Olive oil, coconut oil, sweet almond oil, castor oil, potassium hydroxide, water, musk fragrance</t>
         </is>
       </c>
       <c r="O23" s="14" t="inlineStr">
@@ -2278,7 +2287,7 @@
       </c>
     </row>
     <row r="24" ht="48" customHeight="1">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>537824641738</t>
         </is>
@@ -2333,12 +2342,12 @@
       </c>
       <c r="M24" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A light shower gel of olive oil, coconut, sweet almond, and castor oil. It cleanses the skin and leaves it soft and moisturized. Oak scent.</t>
+          <t>A light shower gel of olive oil, coconut, sweet almond, and castor oil. It cleanses the skin and leaves it soft and moisturized. Oak scent.</t>
         </is>
       </c>
       <c r="N24" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olive oil, coconut oil, sweet almond oil, castor oil, potassium hydroxide, water, oak fragrance</t>
+          <t>Olive oil, coconut oil, sweet almond oil, castor oil, potassium hydroxide, water, oak fragrance</t>
         </is>
       </c>
       <c r="O24" s="14" t="inlineStr">
@@ -2348,7 +2357,7 @@
       </c>
     </row>
     <row r="25" ht="48" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>889082131939</t>
         </is>
@@ -2403,12 +2412,12 @@
       </c>
       <c r="M25" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A light shower gel of olive oil, coconut, sweet almond, and castor oil. It cleanses the skin and leaves it soft and moisturized. Oud scent.</t>
+          <t>A light shower gel of olive oil, coconut, sweet almond, and castor oil. It cleanses the skin and leaves it soft and moisturized. Oud scent.</t>
         </is>
       </c>
       <c r="N25" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olive oil, coconut oil, sweet almond oil, castor oil, potassium hydroxide, water, oud fragrance</t>
+          <t>Olive oil, coconut oil, sweet almond oil, castor oil, potassium hydroxide, water, oud fragrance</t>
         </is>
       </c>
       <c r="O25" s="14" t="inlineStr">
@@ -2442,7 +2451,7 @@
           <x14:formula1>
             <xm:f>Sheet2!$A$2:$A$395</xm:f>
           </x14:formula1>
-          <xm:sqref>G1:G1048576</xm:sqref>
+          <xm:sqref>G2:G1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
